--- a/src/out_profile_game.xlsx
+++ b/src/out_profile_game.xlsx
@@ -427,7 +427,7 @@
         <v>Game ID</v>
       </c>
       <c r="B3" t="str">
-        <v>mt3di2zbwgpgvw</v>
+        <v>mt7qo6vaiq1zib</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +435,7 @@
         <v>Date</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-08-21</v>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="5">
@@ -539,7 +539,7 @@
         <v>Exported</v>
       </c>
       <c r="B17" t="str">
-        <v>8/21/2026, 1:59:35 PM</v>
+        <v>8/24/2026, 3:19:19 PM</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -571,6 +571,7 @@
     <col min="16" max="16" width="9.83203125" customWidth="1"/>
     <col min="17" max="17" width="9.83203125" customWidth="1"/>
     <col min="18" max="18" width="9.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,48 +585,51 @@
         <v>Pos</v>
       </c>
       <c r="D1" t="str">
+        <v>Minutes</v>
+      </c>
+      <c r="E1" t="str">
         <v>Goals</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Shots</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Shot %</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Assists</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Steals</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Blocks</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Turnovers</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>7's Drawn</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>7's Made</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>7's Missed</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>2 Min</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>2's Drawn</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Yellow</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Red</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Points</v>
       </c>
     </row>
@@ -634,26 +638,26 @@
         <v>7</v>
       </c>
       <c r="B2" t="str">
-        <v>Tierney</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="C2" t="str">
         <v>CB</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
@@ -682,6 +686,9 @@
         <v>0</v>
       </c>
       <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
     </row>
@@ -695,21 +702,21 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>100</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
@@ -738,19 +745,22 @@
         <v>0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -761,6 +771,7 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,10 +802,13 @@
       <c r="I1" t="str">
         <v>Saves After Whistle</v>
       </c>
+      <c r="J1" t="str">
+        <v>Empty Net Goals</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1007,7 +1021,7 @@
         <v>H1</v>
       </c>
       <c r="C2" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D2" t="str">
         <v>Air Force</v>
@@ -1016,7 +1030,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="str">
-        <v>Tierney</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="G2" t="str">
         <v>GOAL</v>
@@ -1042,7 +1056,7 @@
         <v>H1</v>
       </c>
       <c r="C3" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D3" t="str">
         <v>Air Force</v>
@@ -1051,7 +1065,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="str">
-        <v>Tierney</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="G3" t="str">
         <v>GOAL</v>
@@ -1077,7 +1091,7 @@
         <v>H1</v>
       </c>
       <c r="C4" t="str">
-        <v>00:00</v>
+        <v>30:00</v>
       </c>
       <c r="D4" t="str">
         <v>Air Force</v>
@@ -1086,7 +1100,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="str">
-        <v>Tierney</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="G4" t="str">
         <v>assist</v>
@@ -1113,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -1160,12 +1174,15 @@
         <v>Y %</v>
       </c>
       <c r="K1" t="str">
+        <v>Note</v>
+      </c>
+      <c r="L1" t="str">
         <v>(X/Y are % of the goal-map image, from the keeper's left)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1203,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="str">
-        <v>Tierney</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="C2" t="str">
         <v>CB</v>
